--- a/data/processed/positivacao/2024-07_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2024-07_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -26141,7 +26141,7 @@
     <row r="993">
       <c r="A993" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B993" t="inlineStr"/>
@@ -37337,7 +37337,7 @@
     <row r="1424">
       <c r="A1424" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1424" t="inlineStr"/>
@@ -65891,7 +65891,7 @@
     <row r="2523">
       <c r="A2523" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2523" t="inlineStr"/>
@@ -67562,12 +67562,12 @@
       <c r="A2588" t="inlineStr"/>
       <c r="B2588" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 5 cliente(s), não positivou 84 cliente(s) - Total vendido: R$ 3.973,06
+          <t>Vendedor 1 - VENDEDOR 01: positivou 5 cliente(s), não positivou 84 cliente(s) - Total vendido: R$ 3.973,06
 Vendedor 18 - LOJA: positivou 174 cliente(s), não positivou 720 cliente(s) - Total vendido: R$ 71.895,19
-Vendedor 3 - FERNANDA: positivou 102 cliente(s), não positivou 328 cliente(s) - Total vendido: R$ 154.740,86
-Vendedor 4 - DANIELA: positivou 102 cliente(s), não positivou 550 cliente(s) - Total vendido: R$ 53.983,34
+Vendedor 3 - VENDEDOR 03: positivou 102 cliente(s), não positivou 328 cliente(s) - Total vendido: R$ 154.740,86
+Vendedor 4 - VENDEDOR 04: positivou 102 cliente(s), não positivou 550 cliente(s) - Total vendido: R$ 53.983,34
 Vendedor 5 - SITE: positivou 6 cliente(s), não positivou 439 cliente(s) - Total vendido: R$ 1.593,90
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2588" t="inlineStr"/>
